--- a/docs/StructureDefinition-PASportObservationGaitCycle.xlsx
+++ b/docs/StructureDefinition-PASportObservationGaitCycle.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T05:34:23+08:00</t>
+    <t>2026-02-28T07:16:04+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PASportObservationGaitCycle.xlsx
+++ b/docs/StructureDefinition-PASportObservationGaitCycle.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T07:16:04+08:00</t>
+    <t>2026-02-28T23:13:53+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PASportObservationGaitCycle.xlsx
+++ b/docs/StructureDefinition-PASportObservationGaitCycle.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.1</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T23:13:53+08:00</t>
+    <t>2026-03-01T19:25:35+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PASportObservationGaitCycle.xlsx
+++ b/docs/StructureDefinition-PASportObservationGaitCycle.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T19:25:35+08:00</t>
+    <t>2026-03-02T02:26:08+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PASportObservationGaitCycle.xlsx
+++ b/docs/StructureDefinition-PASportObservationGaitCycle.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5478" uniqueCount="730">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5478" uniqueCount="732">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T02:26:08+08:00</t>
+    <t>2026-04-02T13:32:15+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -269,10 +269,10 @@
 </t>
   </si>
   <si>
-    <t>Measurements and simple assertions</t>
-  </si>
-  <si>
-    <t>Measurements and simple assertions made about a patient, device or other subject.</t>
+    <t>通用檢驗檢查結果或發現的測量和簡單聲明</t>
+  </si>
+  <si>
+    <t>關於患者的通用檢驗檢查結果測量和簡單聲明，包括由設備或醫護人員觀察到的發現。</t>
   </si>
   <si>
     <t>Used for simple observations such as device measurements, laboratory atomic results, vital signs, height, weight, smoking status, comments, etc.  Other resources are used to provide context for observations such as laboratory reports, etc.</t>
@@ -346,10 +346,10 @@
 </t>
   </si>
   <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+    <t>創建此內容所依據的一組規則</t>
+  </si>
+  <si>
+    <t>構建 resource 時遵循的一系列規則的參照，在處理內容時必須理解這些規則。通常這是對 IG 所定義之特殊規則及其他 profiles 的參照。</t>
   </si>
   <si>
     <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
@@ -380,7 +380,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -520,10 +520,10 @@
 </t>
   </si>
   <si>
-    <t>Fulfills plan, proposal or order</t>
-  </si>
-  <si>
-    <t>A plan, proposal or order that is fulfilled in whole or in part by this event.  For example, a MedicationRequest may require a patient to have laboratory test performed before  it is dispensed.</t>
+    <t>檢驗檢查的依據</t>
+  </si>
+  <si>
+    <t>產生此檢驗檢查的計畫或請求。</t>
   </si>
   <si>
     <t>Allows tracing of authorization for the event and tracking whether proposals/recommendations were acted upon.</t>
@@ -549,10 +549,10 @@
 </t>
   </si>
   <si>
-    <t>Part of referenced event</t>
-  </si>
-  <si>
-    <t>A larger event of which this particular Observation is a component or step.  For example,  an observation as part of a procedure.</t>
+    <t>作為較大項目的一部分</t>
+  </si>
+  <si>
+    <t>表示此檢驗檢查是其他資源的一部分，例如：用藥給藥、調劑、用藥聲明、處置、免疫接種或影像檢查。</t>
   </si>
   <si>
     <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
@@ -573,7 +573,7 @@
     <t>registered | preliminary | final | amended +</t>
   </si>
   <si>
-    <t>The status of the result value.</t>
+    <t>該項檢驗檢查的狀態。</t>
   </si>
   <si>
     <t>This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
@@ -613,10 +613,10 @@
 </t>
   </si>
   <si>
-    <t>Classification of  type of observation</t>
-  </si>
-  <si>
-    <t>A code that classifies the general type of observation being made.</t>
+    <t>檢驗檢查的分類</t>
+  </si>
+  <si>
+    <t>檢驗檢查的分類。</t>
   </si>
   <si>
     <t>In addition to the required category valueset, this element allows various categorization schemes based on the owner’s definition of the category and effectively multiple categories can be used at once.  The level of granularity is defined by the category concepts in the value set.</t>
@@ -628,7 +628,7 @@
     <t>Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">pattern:$this}
@@ -654,7 +654,13 @@
 </t>
   </si>
   <si>
-    <t>此slice綁定的值集之綁定強度雖為最高強度「要求使用(Requird)」，但因slice之特性，其不會限制僅能填此值集中的代碼，故在實作時也可使用其他值集的代碼。</t>
+    <t>臺灣核心分類</t>
+  </si>
+  <si>
+    <t>臺灣核心檢驗檢查分類。</t>
+  </si>
+  <si>
+    <t>此 slice 綁定的值集之綁定強度雖為最高強度「要求使用 (Requird)」，但因 slice 之特性，其不會限制僅能填此值集中的代碼，故在實作時也可使用其他值集的代碼。</t>
   </si>
   <si>
     <t>https://twcore.mohw.gov.tw/ig/twcore/ValueSet/category-code-tw</t>
@@ -917,13 +923,13 @@
 </t>
   </si>
   <si>
-    <t>概念（Concept）— 參照一個專門術語或只是文字表述</t>
-  </si>
-  <si>
-    <t>A concept that may be defined by a formal reference to a terminology or ontology or may be provided by text.</t>
-  </si>
-  <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
+    <t>檢驗檢查類型</t>
+  </si>
+  <si>
+    <t>描述該檢驗檢查所測量的內容</t>
+  </si>
+  <si>
+    <t>*All* code-value and, if present, component.code-component.value pairs need to be taken into account to correctly understand the meaning of the observation.</t>
   </si>
   <si>
     <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
@@ -935,14 +941,22 @@
     <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>CE/CNE/CWE</t>
-  </si>
-  <si>
-    <t>CD</t>
+    <t>Event.code</t>
+  </si>
+  <si>
+    <t>&lt; 363787002 |Observable entity| OR &lt; 386053000 |Evaluation procedure|</t>
+  </si>
+  <si>
+    <t>OBX-3</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>FiveWs.what[x]</t>
+  </si>
+  <si>
+    <t>116680003 |Is a|</t>
   </si>
   <si>
     <t>Observation.code.id</t>
@@ -979,12 +993,6 @@
     <t>允許代碼系統中的替代編碼，以及翻譯到其他編碼系統。</t>
   </si>
   <si>
-    <t>CE/CNE/CWE subset one of the sets of component 1-3 or 4-6</t>
-  </si>
-  <si>
-    <t>CV</t>
-  </si>
-  <si>
     <t>Observation.code.coding.id</t>
   </si>
   <si>
@@ -1100,7 +1108,7 @@
     <t>量測對象</t>
   </si>
   <si>
-    <t>The patient, or group of patients, location, or device this observation is about and into whose record the observation is placed. If the actual focus of the observation is different from the subject (or a sample of, part, or region of the subject), the `focus` element or the `code` itself specifies the actual focus of the observation.</t>
+    <t>檢驗檢查關注的主體 (如患者、群組、設備或位置)。</t>
   </si>
   <si>
     <t>One would expect this element to be a cardinality of 1..1. The only circumstance in which the subject can be missing is when the observation is made by a device that does not know the patient. In this case, the observation SHALL be matched to a patient through some context/channel matching technique, and at this point, the observation should be updated.</t>
@@ -1210,7 +1218,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1221,9 +1229,6 @@
   </si>
   <si>
     <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](http://hl7.org/fhir/R4/extension-observation-focuscode.html).</t>
-  </si>
-  <si>
-    <t>OBX-3</t>
   </si>
   <si>
     <t>participation[typeCode=SBJ]</t>
@@ -1240,10 +1245,10 @@
 </t>
   </si>
   <si>
-    <t>Healthcare event during which this observation is made</t>
-  </si>
-  <si>
-    <t>The healthcare event  (e.g. a patient and healthcare provider interaction) during which this observation is made.</t>
+    <t>與此檢驗檢查相關的就醫事件</t>
+  </si>
+  <si>
+    <t>此檢驗檢查是在哪個就醫情境產生的。</t>
   </si>
   <si>
     <t>This will typically be the encounter the event occurred within, but some events may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter (e.g. pre-admission laboratory tests).</t>
@@ -1275,10 +1280,10 @@
 PeriodTiminginstant</t>
   </si>
   <si>
-    <t>Clinically relevant time/time-period for observation</t>
-  </si>
-  <si>
-    <t>The time or time-period the observed value is asserted as being true. For biological subjects - e.g. human patients - this is usually called the "physiologically relevant time". This is usually either the time of the procedure or of specimen collection, but very often the source of the date/time is not known, only the date/time itself.</t>
+    <t>檢驗檢查的時間或時段</t>
+  </si>
+  <si>
+    <t>檢驗檢查進行的時間點或時間段。</t>
   </si>
   <si>
     <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/R4/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
@@ -1334,7 +1339,7 @@
     <t>量測人員</t>
   </si>
   <si>
-    <t>Who was responsible for asserting the observed value as "true".</t>
+    <t>執行或負責檢驗檢查的人員。</t>
   </si>
   <si>
     <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
@@ -1380,10 +1385,10 @@
 CodeableConceptstringbooleanintegerRangeRatioSampledDatatimedateTimePeriod</t>
   </si>
   <si>
-    <t>Actual result</t>
-  </si>
-  <si>
-    <t>The information determined as a result of making the observation, if the information has a simple value.</t>
+    <t>檢驗檢查的結果值</t>
+  </si>
+  <si>
+    <t>檢驗檢查或觀察的實際結果。</t>
   </si>
   <si>
     <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
@@ -1427,7 +1432,7 @@
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">obs-6
@@ -1459,7 +1464,7 @@
     <t>Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1558,10 +1563,10 @@
 </t>
   </si>
   <si>
-    <t>Specimen used for this observation</t>
-  </si>
-  <si>
-    <t>The specimen that was used when this observation was made.</t>
+    <t>檢驗檢查的檢體</t>
+  </si>
+  <si>
+    <t>進行檢驗檢查的檢體。</t>
   </si>
   <si>
     <t>Should only be used if not implicit in code found in `Observation.code`.  Observations are not made on specimens themselves; they are made on a subject, but in many cases by the means of a specimen. Note that although specimens are often involved, they are not always tracked and reported explicitly. Also note that observation resources may be used in contexts that track the specimen explicitly (e.g. Diagnostic Report).</t>
@@ -1582,7 +1587,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1662,7 +1667,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1712,7 +1717,7 @@
     <t>Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1748,7 +1753,7 @@
     <t>Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1789,10 +1794,10 @@
 </t>
   </si>
   <si>
-    <t>Related resource that belongs to the Observation group</t>
-  </si>
-  <si>
-    <t>This observation is a group observation (e.g. a battery, a panel of tests, a set of vital sign measurements) that includes the target as a member of the group.</t>
+    <t>包含的相關檢驗檢查</t>
+  </si>
+  <si>
+    <t>與此檢驗檢查相關聯的其他檢驗檢查或問卷回應。</t>
   </si>
   <si>
     <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
@@ -1811,10 +1816,10 @@
 </t>
   </si>
   <si>
-    <t>Related measurements the observation is made from</t>
-  </si>
-  <si>
-    <t>The target resource that represents a measurement from which this observation value is derived. For example, a calculated anion gap or a fetal measurement based on an ultrasound image.</t>
+    <t>觀察來源或依據</t>
+  </si>
+  <si>
+    <t>用於獲取此觀察結果的參考資源，如：來源觀察、文件引用、問卷回應等。</t>
   </si>
   <si>
     <t>All the reference choices that are listed in this element can represent clinical observations and other measurements that may be the source for a derived value.  The most common reference will be another Observation.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.</t>
@@ -1875,20 +1880,20 @@
     <t>*All* code-value and  component.code-component.value pairs need to be taken into account to correctly understand the meaning of the observation.</t>
   </si>
   <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
+  </si>
+  <si>
     <t>&lt; 363787002 |Observable entity| OR  &lt; 386053000 |Evaluation procedure|</t>
   </si>
   <si>
-    <t>code</t>
-  </si>
-  <si>
-    <t>FiveWs.what[x]</t>
-  </si>
-  <si>
     <t>Observation.component.value[x]</t>
   </si>
   <si>
     <t>Actual component result</t>
+  </si>
+  <si>
+    <t>The information determined as a result of making the observation, if the information has a simple value.</t>
   </si>
   <si>
     <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
@@ -2624,7 +2629,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="114.32421875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="116.8203125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="52.62109375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.0625" customWidth="true" bestFit="true"/>
@@ -4486,10 +4491,10 @@
         <v>203</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="N16" t="s" s="2">
         <v>193</v>
@@ -4523,10 +4528,10 @@
         <v>181</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>20</v>
@@ -4579,10 +4584,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4605,13 +4610,13 @@
         <v>20</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4662,7 +4667,7 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4686,7 +4691,7 @@
         <v>20</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>20</v>
@@ -4697,10 +4702,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4729,7 +4734,7 @@
         <v>139</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>141</v>
@@ -4770,10 +4775,10 @@
         <v>20</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>20</v>
@@ -4782,7 +4787,7 @@
         <v>198</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4806,7 +4811,7 @@
         <v>20</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>20</v>
@@ -4817,10 +4822,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4843,19 +4848,19 @@
         <v>93</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>20</v>
@@ -4904,7 +4909,7 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4925,10 +4930,10 @@
         <v>20</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>20</v>
@@ -4939,10 +4944,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4965,13 +4970,13 @@
         <v>20</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -5022,7 +5027,7 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -5046,7 +5051,7 @@
         <v>20</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>20</v>
@@ -5057,10 +5062,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -5089,7 +5094,7 @@
         <v>139</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>141</v>
@@ -5130,10 +5135,10 @@
         <v>20</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>20</v>
@@ -5142,7 +5147,7 @@
         <v>198</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -5166,7 +5171,7 @@
         <v>20</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>20</v>
@@ -5177,10 +5182,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5206,16 +5211,16 @@
         <v>106</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>20</v>
@@ -5225,7 +5230,7 @@
         <v>20</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="T22" t="s" s="2">
         <v>20</v>
@@ -5264,7 +5269,7 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -5285,10 +5290,10 @@
         <v>20</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>20</v>
@@ -5299,10 +5304,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5325,16 +5330,16 @@
         <v>93</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -5384,7 +5389,7 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -5405,10 +5410,10 @@
         <v>20</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>20</v>
@@ -5419,10 +5424,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5448,14 +5453,14 @@
         <v>112</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>20</v>
@@ -5465,7 +5470,7 @@
         <v>20</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>20</v>
@@ -5504,7 +5509,7 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -5525,10 +5530,10 @@
         <v>20</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>20</v>
@@ -5539,10 +5544,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5565,17 +5570,17 @@
         <v>93</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>20</v>
@@ -5585,7 +5590,7 @@
         <v>20</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>20</v>
@@ -5624,7 +5629,7 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5645,10 +5650,10 @@
         <v>20</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>20</v>
@@ -5659,10 +5664,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5685,19 +5690,19 @@
         <v>93</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>20</v>
@@ -5746,7 +5751,7 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5767,10 +5772,10 @@
         <v>20</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>20</v>
@@ -5781,10 +5786,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5807,19 +5812,19 @@
         <v>93</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>20</v>
@@ -5868,7 +5873,7 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5889,10 +5894,10 @@
         <v>20</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>20</v>
@@ -5903,14 +5908,14 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5926,22 +5931,22 @@
         <v>20</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="K28" t="s" s="2">
         <v>190</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>20</v>
@@ -5969,10 +5974,10 @@
         <v>116</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>20</v>
@@ -5990,7 +5995,7 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>92</v>
@@ -5999,36 +6004,36 @@
         <v>92</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>296</v>
+        <v>20</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>20</v>
+        <v>298</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>20</v>
+        <v>299</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>20</v>
+        <v>302</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>20</v>
+        <v>303</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6051,13 +6056,13 @@
         <v>20</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -6108,7 +6113,7 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -6132,7 +6137,7 @@
         <v>20</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>20</v>
@@ -6143,10 +6148,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6172,10 +6177,10 @@
         <v>138</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -6214,10 +6219,10 @@
         <v>20</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>20</v>
@@ -6226,7 +6231,7 @@
         <v>198</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -6261,10 +6266,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6284,22 +6289,22 @@
         <v>20</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>20</v>
@@ -6348,7 +6353,7 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -6357,7 +6362,7 @@
         <v>81</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>296</v>
+        <v>20</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>104</v>
@@ -6369,10 +6374,10 @@
         <v>20</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>310</v>
+        <v>229</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>311</v>
+        <v>230</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>20</v>
@@ -6383,10 +6388,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6409,13 +6414,13 @@
         <v>20</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6466,7 +6471,7 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -6490,7 +6495,7 @@
         <v>20</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>20</v>
@@ -6501,10 +6506,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6530,13 +6535,13 @@
         <v>138</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6574,10 +6579,10 @@
         <v>20</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>20</v>
@@ -6586,7 +6591,7 @@
         <v>198</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6621,10 +6626,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6650,16 +6655,16 @@
         <v>106</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>20</v>
@@ -6669,7 +6674,7 @@
         <v>20</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>20</v>
@@ -6708,7 +6713,7 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6729,10 +6734,10 @@
         <v>20</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>20</v>
@@ -6743,10 +6748,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6769,16 +6774,16 @@
         <v>93</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6828,7 +6833,7 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6849,10 +6854,10 @@
         <v>20</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>20</v>
@@ -6863,10 +6868,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6892,14 +6897,14 @@
         <v>112</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -6909,7 +6914,7 @@
         <v>20</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>20</v>
@@ -6948,7 +6953,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6969,10 +6974,10 @@
         <v>20</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>20</v>
@@ -6983,10 +6988,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7009,17 +7014,17 @@
         <v>93</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>20</v>
@@ -7029,7 +7034,7 @@
         <v>20</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="T37" t="s" s="2">
         <v>20</v>
@@ -7068,7 +7073,7 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -7089,10 +7094,10 @@
         <v>20</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>20</v>
@@ -7103,10 +7108,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7129,19 +7134,19 @@
         <v>93</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>20</v>
@@ -7190,7 +7195,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -7211,10 +7216,10 @@
         <v>20</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>20</v>
@@ -7225,10 +7230,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7251,19 +7256,19 @@
         <v>93</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>20</v>
@@ -7312,7 +7317,7 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -7333,10 +7338,10 @@
         <v>20</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>20</v>
@@ -7347,10 +7352,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7373,19 +7378,19 @@
         <v>93</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>20</v>
@@ -7434,7 +7439,7 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -7449,19 +7454,19 @@
         <v>104</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>20</v>
@@ -7469,10 +7474,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7495,13 +7500,13 @@
         <v>20</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7552,7 +7557,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7576,7 +7581,7 @@
         <v>20</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>20</v>
@@ -7587,10 +7592,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7619,7 +7624,7 @@
         <v>139</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>141</v>
@@ -7660,10 +7665,10 @@
         <v>20</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>20</v>
@@ -7672,7 +7677,7 @@
         <v>198</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7696,7 +7701,7 @@
         <v>20</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>20</v>
@@ -7707,10 +7712,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7733,16 +7738,16 @@
         <v>93</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7792,7 +7797,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7801,7 +7806,7 @@
         <v>92</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>104</v>
@@ -7827,10 +7832,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7856,13 +7861,13 @@
         <v>106</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7888,13 +7893,13 @@
         <v>20</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>20</v>
@@ -7912,7 +7917,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7947,10 +7952,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7976,13 +7981,13 @@
         <v>150</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -8032,7 +8037,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -8056,7 +8061,7 @@
         <v>20</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>20</v>
@@ -8067,10 +8072,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8093,16 +8098,16 @@
         <v>93</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -8152,7 +8157,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -8187,10 +8192,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8213,16 +8218,16 @@
         <v>93</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8272,7 +8277,7 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -8293,13 +8298,13 @@
         <v>20</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>389</v>
+        <v>300</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>20</v>
@@ -8307,14 +8312,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -8333,19 +8338,19 @@
         <v>93</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>20</v>
@@ -8394,7 +8399,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8409,19 +8414,19 @@
         <v>104</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>20</v>
@@ -8429,14 +8434,14 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -8455,19 +8460,19 @@
         <v>93</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>20</v>
@@ -8516,7 +8521,7 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8531,19 +8536,19 @@
         <v>104</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>20</v>
@@ -8551,10 +8556,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8577,16 +8582,16 @@
         <v>93</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8636,7 +8641,7 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8657,13 +8662,13 @@
         <v>20</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>20</v>
@@ -8671,10 +8676,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8697,17 +8702,17 @@
         <v>93</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>20</v>
@@ -8756,7 +8761,7 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8771,19 +8776,19 @@
         <v>104</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>20</v>
@@ -8791,10 +8796,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8817,13 +8822,13 @@
         <v>20</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8874,7 +8879,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8898,7 +8903,7 @@
         <v>20</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>20</v>
@@ -8909,10 +8914,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8941,7 +8946,7 @@
         <v>139</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>141</v>
@@ -8982,10 +8987,10 @@
         <v>20</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>20</v>
@@ -8994,7 +8999,7 @@
         <v>198</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -9018,7 +9023,7 @@
         <v>20</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>20</v>
@@ -9029,10 +9034,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9055,16 +9060,16 @@
         <v>93</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -9114,7 +9119,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -9123,7 +9128,7 @@
         <v>92</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>104</v>
@@ -9149,10 +9154,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9178,13 +9183,13 @@
         <v>106</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9210,13 +9215,13 @@
         <v>20</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>20</v>
@@ -9234,7 +9239,7 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -9269,10 +9274,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9298,13 +9303,13 @@
         <v>150</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9354,7 +9359,7 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9378,7 +9383,7 @@
         <v>20</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>20</v>
@@ -9389,10 +9394,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9415,16 +9420,16 @@
         <v>93</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9474,7 +9479,7 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9509,10 +9514,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9535,19 +9540,19 @@
         <v>93</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>20</v>
@@ -9596,7 +9601,7 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9605,7 +9610,7 @@
         <v>92</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>104</v>
@@ -9614,27 +9619,27 @@
         <v>20</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9660,16 +9665,16 @@
         <v>203</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>20</v>
@@ -9694,13 +9699,13 @@
         <v>20</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>20</v>
@@ -9718,7 +9723,7 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9727,7 +9732,7 @@
         <v>92</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>104</v>
@@ -9742,7 +9747,7 @@
         <v>135</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>20</v>
@@ -9753,14 +9758,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9782,16 +9787,16 @@
         <v>203</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>20</v>
@@ -9816,13 +9821,13 @@
         <v>20</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>20</v>
@@ -9840,7 +9845,7 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9858,27 +9863,27 @@
         <v>20</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9901,19 +9906,19 @@
         <v>20</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>20</v>
@@ -9962,7 +9967,7 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9983,10 +9988,10 @@
         <v>20</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>20</v>
@@ -9997,10 +10002,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10026,13 +10031,13 @@
         <v>203</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -10058,11 +10063,11 @@
         <v>20</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Y62" s="2"/>
       <c r="Z62" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>20</v>
@@ -10080,7 +10085,7 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -10098,27 +10103,27 @@
         <v>20</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10144,16 +10149,16 @@
         <v>203</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>20</v>
@@ -10178,11 +10183,11 @@
         <v>20</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Y63" s="2"/>
       <c r="Z63" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>20</v>
@@ -10200,7 +10205,7 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -10221,10 +10226,10 @@
         <v>20</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>20</v>
@@ -10235,10 +10240,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10261,16 +10266,16 @@
         <v>20</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -10320,7 +10325,7 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -10338,27 +10343,27 @@
         <v>20</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10381,16 +10386,16 @@
         <v>20</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10440,7 +10445,7 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10458,27 +10463,27 @@
         <v>20</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10501,19 +10506,19 @@
         <v>20</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>20</v>
@@ -10562,7 +10567,7 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10574,7 +10579,7 @@
         <v>20</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>20</v>
@@ -10583,10 +10588,10 @@
         <v>20</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>20</v>
@@ -10597,10 +10602,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10623,13 +10628,13 @@
         <v>20</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10680,7 +10685,7 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10704,7 +10709,7 @@
         <v>20</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>20</v>
@@ -10715,10 +10720,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10747,7 +10752,7 @@
         <v>139</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N68" t="s" s="2">
         <v>141</v>
@@ -10800,7 +10805,7 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10824,7 +10829,7 @@
         <v>20</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>20</v>
@@ -10835,14 +10840,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -10864,10 +10869,10 @@
         <v>138</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>141</v>
@@ -10922,7 +10927,7 @@
         <v>20</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10957,10 +10962,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10983,13 +10988,13 @@
         <v>20</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -11040,7 +11045,7 @@
         <v>20</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -11049,7 +11054,7 @@
         <v>92</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>104</v>
@@ -11061,10 +11066,10 @@
         <v>20</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>20</v>
@@ -11075,10 +11080,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11101,13 +11106,13 @@
         <v>20</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -11158,7 +11163,7 @@
         <v>20</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -11167,7 +11172,7 @@
         <v>92</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>104</v>
@@ -11179,10 +11184,10 @@
         <v>20</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>20</v>
@@ -11193,10 +11198,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11222,16 +11227,16 @@
         <v>203</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>20</v>
@@ -11259,10 +11264,10 @@
         <v>116</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>20</v>
@@ -11280,7 +11285,7 @@
         <v>20</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -11298,13 +11303,13 @@
         <v>20</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>20</v>
@@ -11315,10 +11320,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11344,16 +11349,16 @@
         <v>203</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>20</v>
@@ -11378,13 +11383,13 @@
         <v>20</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>20</v>
@@ -11402,7 +11407,7 @@
         <v>20</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11420,13 +11425,13 @@
         <v>20</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>20</v>
@@ -11437,10 +11442,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11463,17 +11468,17 @@
         <v>20</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>20</v>
@@ -11522,7 +11527,7 @@
         <v>20</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11546,7 +11551,7 @@
         <v>20</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>20</v>
@@ -11557,10 +11562,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11583,13 +11588,13 @@
         <v>20</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11640,7 +11645,7 @@
         <v>20</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11661,10 +11666,10 @@
         <v>20</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>20</v>
@@ -11675,10 +11680,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11701,16 +11706,16 @@
         <v>93</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11760,7 +11765,7 @@
         <v>20</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11781,10 +11786,10 @@
         <v>20</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>20</v>
@@ -11795,10 +11800,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11821,16 +11826,16 @@
         <v>93</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11880,7 +11885,7 @@
         <v>20</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11901,10 +11906,10 @@
         <v>20</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>20</v>
@@ -11915,10 +11920,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11926,10 +11931,10 @@
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>93</v>
@@ -11941,19 +11946,19 @@
         <v>93</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>20</v>
@@ -11990,10 +11995,10 @@
         <v>20</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="AC78" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="AD78" t="s" s="2">
         <v>20</v>
@@ -12002,7 +12007,7 @@
         <v>198</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -12023,10 +12028,10 @@
         <v>20</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>20</v>
@@ -12037,10 +12042,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12063,13 +12068,13 @@
         <v>20</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -12120,7 +12125,7 @@
         <v>20</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -12144,7 +12149,7 @@
         <v>20</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>20</v>
@@ -12155,10 +12160,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12187,7 +12192,7 @@
         <v>139</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N80" t="s" s="2">
         <v>141</v>
@@ -12240,7 +12245,7 @@
         <v>20</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -12264,7 +12269,7 @@
         <v>20</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>20</v>
@@ -12275,14 +12280,14 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -12304,10 +12309,10 @@
         <v>138</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="N81" t="s" s="2">
         <v>141</v>
@@ -12362,7 +12367,7 @@
         <v>20</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12397,10 +12402,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12426,16 +12431,16 @@
         <v>203</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>20</v>
@@ -12460,13 +12465,13 @@
         <v>20</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>295</v>
+        <v>598</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>20</v>
@@ -12484,7 +12489,7 @@
         <v>20</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>92</v>
@@ -12502,16 +12507,16 @@
         <v>20</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>389</v>
+        <v>300</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>597</v>
+        <v>301</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>598</v>
+        <v>302</v>
       </c>
       <c r="AP82" t="s" s="2">
         <v>20</v>
@@ -12519,10 +12524,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12545,19 +12550,19 @@
         <v>93</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>440</v>
+        <v>602</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>20</v>
@@ -12606,7 +12611,7 @@
         <v>20</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12624,27 +12629,27 @@
         <v>20</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12670,16 +12675,16 @@
         <v>203</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>20</v>
@@ -12704,13 +12709,13 @@
         <v>20</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>20</v>
@@ -12728,7 +12733,7 @@
         <v>20</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12737,7 +12742,7 @@
         <v>92</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>104</v>
@@ -12752,7 +12757,7 @@
         <v>135</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>20</v>
@@ -12763,14 +12768,14 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -12792,16 +12797,16 @@
         <v>203</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>20</v>
@@ -12826,13 +12831,13 @@
         <v>20</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>20</v>
@@ -12850,7 +12855,7 @@
         <v>20</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12868,27 +12873,27 @@
         <v>20</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12914,16 +12919,16 @@
         <v>82</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>20</v>
@@ -12972,7 +12977,7 @@
         <v>20</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12993,10 +12998,10 @@
         <v>20</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>20</v>
@@ -13007,13 +13012,13 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="D87" t="s" s="2">
         <v>20</v>
@@ -13035,19 +13040,19 @@
         <v>93</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>20</v>
@@ -13096,7 +13101,7 @@
         <v>20</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -13117,10 +13122,10 @@
         <v>20</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>20</v>
@@ -13131,10 +13136,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13157,13 +13162,13 @@
         <v>20</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -13214,7 +13219,7 @@
         <v>20</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -13238,7 +13243,7 @@
         <v>20</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>20</v>
@@ -13249,10 +13254,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13281,7 +13286,7 @@
         <v>139</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N89" t="s" s="2">
         <v>141</v>
@@ -13334,7 +13339,7 @@
         <v>20</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -13358,7 +13363,7 @@
         <v>20</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>20</v>
@@ -13369,14 +13374,14 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -13398,10 +13403,10 @@
         <v>138</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="N90" t="s" s="2">
         <v>141</v>
@@ -13456,7 +13461,7 @@
         <v>20</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13491,10 +13496,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13520,16 +13525,16 @@
         <v>203</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>20</v>
@@ -13554,13 +13559,13 @@
         <v>20</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>295</v>
+        <v>598</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>20</v>
@@ -13578,7 +13583,7 @@
         <v>20</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>92</v>
@@ -13596,16 +13601,16 @@
         <v>20</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>389</v>
+        <v>300</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>597</v>
+        <v>301</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>598</v>
+        <v>302</v>
       </c>
       <c r="AP91" t="s" s="2">
         <v>20</v>
@@ -13613,10 +13618,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13639,13 +13644,13 @@
         <v>20</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13696,7 +13701,7 @@
         <v>20</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13720,7 +13725,7 @@
         <v>20</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>20</v>
@@ -13731,10 +13736,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13763,7 +13768,7 @@
         <v>139</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N93" t="s" s="2">
         <v>141</v>
@@ -13804,10 +13809,10 @@
         <v>20</v>
       </c>
       <c r="AB93" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AC93" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AD93" t="s" s="2">
         <v>20</v>
@@ -13816,7 +13821,7 @@
         <v>198</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13840,7 +13845,7 @@
         <v>20</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>20</v>
@@ -13851,10 +13856,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13877,19 +13882,19 @@
         <v>93</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>20</v>
@@ -13938,7 +13943,7 @@
         <v>20</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13959,10 +13964,10 @@
         <v>20</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>20</v>
@@ -13973,10 +13978,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13999,13 +14004,13 @@
         <v>20</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -14056,7 +14061,7 @@
         <v>20</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -14080,7 +14085,7 @@
         <v>20</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>20</v>
@@ -14091,10 +14096,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14123,7 +14128,7 @@
         <v>139</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N96" t="s" s="2">
         <v>141</v>
@@ -14164,10 +14169,10 @@
         <v>20</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AC96" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AD96" t="s" s="2">
         <v>20</v>
@@ -14176,7 +14181,7 @@
         <v>198</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -14200,7 +14205,7 @@
         <v>20</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>20</v>
@@ -14211,10 +14216,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14240,16 +14245,16 @@
         <v>106</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>20</v>
@@ -14259,7 +14264,7 @@
         <v>20</v>
       </c>
       <c r="S97" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="T97" t="s" s="2">
         <v>20</v>
@@ -14298,7 +14303,7 @@
         <v>20</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -14319,10 +14324,10 @@
         <v>20</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>20</v>
@@ -14333,10 +14338,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14359,16 +14364,16 @@
         <v>93</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -14418,7 +14423,7 @@
         <v>20</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -14439,10 +14444,10 @@
         <v>20</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>20</v>
@@ -14453,10 +14458,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14482,14 +14487,14 @@
         <v>112</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>20</v>
@@ -14538,7 +14543,7 @@
         <v>20</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14559,10 +14564,10 @@
         <v>20</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>20</v>
@@ -14573,10 +14578,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14599,17 +14604,17 @@
         <v>93</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>20</v>
@@ -14619,7 +14624,7 @@
         <v>20</v>
       </c>
       <c r="S100" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="T100" t="s" s="2">
         <v>20</v>
@@ -14658,7 +14663,7 @@
         <v>20</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14679,10 +14684,10 @@
         <v>20</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>20</v>
@@ -14693,10 +14698,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14719,19 +14724,19 @@
         <v>93</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>20</v>
@@ -14780,7 +14785,7 @@
         <v>20</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14801,10 +14806,10 @@
         <v>20</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>20</v>
@@ -14815,10 +14820,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14841,19 +14846,19 @@
         <v>93</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>20</v>
@@ -14902,7 +14907,7 @@
         <v>20</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14923,10 +14928,10 @@
         <v>20</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>20</v>
@@ -14937,10 +14942,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14963,19 +14968,19 @@
         <v>93</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>440</v>
+        <v>602</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>20</v>
@@ -15012,7 +15017,7 @@
         <v>20</v>
       </c>
       <c r="AB103" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="AC103" s="2"/>
       <c r="AD103" t="s" s="2">
@@ -15022,7 +15027,7 @@
         <v>198</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -15040,30 +15045,30 @@
         <v>20</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP103" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="D104" t="s" s="2">
         <v>20</v>
@@ -15085,19 +15090,19 @@
         <v>93</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>440</v>
+        <v>602</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>20</v>
@@ -15146,7 +15151,7 @@
         <v>20</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -15164,27 +15169,27 @@
         <v>20</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP104" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15207,13 +15212,13 @@
         <v>20</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -15264,7 +15269,7 @@
         <v>20</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -15288,7 +15293,7 @@
         <v>20</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>20</v>
@@ -15299,10 +15304,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15331,7 +15336,7 @@
         <v>139</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N106" t="s" s="2">
         <v>141</v>
@@ -15372,10 +15377,10 @@
         <v>20</v>
       </c>
       <c r="AB106" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AC106" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AD106" t="s" s="2">
         <v>20</v>
@@ -15384,7 +15389,7 @@
         <v>198</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15408,7 +15413,7 @@
         <v>20</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>20</v>
@@ -15419,10 +15424,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15445,19 +15450,19 @@
         <v>93</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>20</v>
@@ -15506,7 +15511,7 @@
         <v>20</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15527,10 +15532,10 @@
         <v>20</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>20</v>
@@ -15541,10 +15546,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15570,20 +15575,20 @@
         <v>112</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q108" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="R108" t="s" s="2">
         <v>20</v>
@@ -15607,10 +15612,10 @@
         <v>181</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>20</v>
@@ -15628,7 +15633,7 @@
         <v>20</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15649,10 +15654,10 @@
         <v>20</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>20</v>
@@ -15663,10 +15668,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15689,17 +15694,17 @@
         <v>93</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>20</v>
@@ -15748,7 +15753,7 @@
         <v>20</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15769,10 +15774,10 @@
         <v>20</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>20</v>
@@ -15783,10 +15788,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15812,14 +15817,14 @@
         <v>106</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>20</v>
@@ -15829,7 +15834,7 @@
         <v>20</v>
       </c>
       <c r="S110" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="T110" t="s" s="2">
         <v>20</v>
@@ -15868,7 +15873,7 @@
         <v>20</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15877,7 +15882,7 @@
         <v>92</v>
       </c>
       <c r="AI110" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="AJ110" t="s" s="2">
         <v>104</v>
@@ -15889,10 +15894,10 @@
         <v>20</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>20</v>
@@ -15903,10 +15908,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15932,16 +15937,16 @@
         <v>112</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>20</v>
@@ -15951,7 +15956,7 @@
         <v>20</v>
       </c>
       <c r="S111" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="T111" t="s" s="2">
         <v>20</v>
@@ -15990,7 +15995,7 @@
         <v>20</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -16011,10 +16016,10 @@
         <v>20</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>20</v>
@@ -16025,10 +16030,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16054,16 +16059,16 @@
         <v>203</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>20</v>
@@ -16088,13 +16093,13 @@
         <v>20</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>20</v>
@@ -16112,7 +16117,7 @@
         <v>20</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -16121,7 +16126,7 @@
         <v>92</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="AJ112" t="s" s="2">
         <v>104</v>
@@ -16136,7 +16141,7 @@
         <v>135</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>20</v>
@@ -16147,14 +16152,14 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
@@ -16176,16 +16181,16 @@
         <v>203</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>20</v>
@@ -16210,13 +16215,13 @@
         <v>20</v>
       </c>
       <c r="X113" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>20</v>
@@ -16234,7 +16239,7 @@
         <v>20</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -16252,27 +16257,27 @@
         <v>20</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP113" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16298,16 +16303,16 @@
         <v>82</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>20</v>
@@ -16356,7 +16361,7 @@
         <v>20</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -16377,10 +16382,10 @@
         <v>20</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>20</v>
@@ -16391,13 +16396,13 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="D115" t="s" s="2">
         <v>20</v>
@@ -16419,19 +16424,19 @@
         <v>93</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>20</v>
@@ -16480,7 +16485,7 @@
         <v>20</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -16501,10 +16506,10 @@
         <v>20</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>20</v>
@@ -16515,10 +16520,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16541,13 +16546,13 @@
         <v>20</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -16598,7 +16603,7 @@
         <v>20</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -16622,7 +16627,7 @@
         <v>20</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>20</v>
@@ -16633,10 +16638,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16665,7 +16670,7 @@
         <v>139</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N117" t="s" s="2">
         <v>141</v>
@@ -16718,7 +16723,7 @@
         <v>20</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -16742,7 +16747,7 @@
         <v>20</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO117" t="s" s="2">
         <v>20</v>
@@ -16753,14 +16758,14 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
@@ -16782,10 +16787,10 @@
         <v>138</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="N118" t="s" s="2">
         <v>141</v>
@@ -16840,7 +16845,7 @@
         <v>20</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -16875,10 +16880,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16904,16 +16909,16 @@
         <v>203</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>20</v>
@@ -16938,13 +16943,13 @@
         <v>20</v>
       </c>
       <c r="X119" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="Y119" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Z119" t="s" s="2">
-        <v>295</v>
+        <v>598</v>
       </c>
       <c r="AA119" t="s" s="2">
         <v>20</v>
@@ -16962,7 +16967,7 @@
         <v>20</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>92</v>
@@ -16980,16 +16985,16 @@
         <v>20</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>389</v>
+        <v>300</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>597</v>
+        <v>301</v>
       </c>
       <c r="AO119" t="s" s="2">
-        <v>598</v>
+        <v>302</v>
       </c>
       <c r="AP119" t="s" s="2">
         <v>20</v>
@@ -16997,10 +17002,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17023,13 +17028,13 @@
         <v>20</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -17080,7 +17085,7 @@
         <v>20</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -17104,7 +17109,7 @@
         <v>20</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>20</v>
@@ -17115,10 +17120,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17147,7 +17152,7 @@
         <v>139</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N121" t="s" s="2">
         <v>141</v>
@@ -17188,10 +17193,10 @@
         <v>20</v>
       </c>
       <c r="AB121" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AC121" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AD121" t="s" s="2">
         <v>20</v>
@@ -17200,7 +17205,7 @@
         <v>198</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -17224,7 +17229,7 @@
         <v>20</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>20</v>
@@ -17235,10 +17240,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17261,19 +17266,19 @@
         <v>93</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>20</v>
@@ -17322,7 +17327,7 @@
         <v>20</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -17343,10 +17348,10 @@
         <v>20</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>20</v>
@@ -17357,10 +17362,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17383,13 +17388,13 @@
         <v>20</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -17440,7 +17445,7 @@
         <v>20</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -17464,7 +17469,7 @@
         <v>20</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>20</v>
@@ -17475,10 +17480,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17507,7 +17512,7 @@
         <v>139</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N124" t="s" s="2">
         <v>141</v>
@@ -17548,10 +17553,10 @@
         <v>20</v>
       </c>
       <c r="AB124" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AC124" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AD124" t="s" s="2">
         <v>20</v>
@@ -17560,7 +17565,7 @@
         <v>198</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -17584,7 +17589,7 @@
         <v>20</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO124" t="s" s="2">
         <v>20</v>
@@ -17595,10 +17600,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17624,16 +17629,16 @@
         <v>106</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>20</v>
@@ -17643,7 +17648,7 @@
         <v>20</v>
       </c>
       <c r="S125" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="T125" t="s" s="2">
         <v>20</v>
@@ -17682,7 +17687,7 @@
         <v>20</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -17703,10 +17708,10 @@
         <v>20</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>20</v>
@@ -17717,10 +17722,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17743,16 +17748,16 @@
         <v>93</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
@@ -17802,7 +17807,7 @@
         <v>20</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -17823,10 +17828,10 @@
         <v>20</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AO126" t="s" s="2">
         <v>20</v>
@@ -17837,10 +17842,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17866,14 +17871,14 @@
         <v>112</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>20</v>
@@ -17883,7 +17888,7 @@
         <v>20</v>
       </c>
       <c r="S127" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="T127" t="s" s="2">
         <v>20</v>
@@ -17922,7 +17927,7 @@
         <v>20</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -17943,10 +17948,10 @@
         <v>20</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AO127" t="s" s="2">
         <v>20</v>
@@ -17957,10 +17962,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17983,17 +17988,17 @@
         <v>93</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>20</v>
@@ -18003,7 +18008,7 @@
         <v>20</v>
       </c>
       <c r="S128" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="T128" t="s" s="2">
         <v>20</v>
@@ -18042,7 +18047,7 @@
         <v>20</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -18063,10 +18068,10 @@
         <v>20</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AO128" t="s" s="2">
         <v>20</v>
@@ -18077,10 +18082,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18103,19 +18108,19 @@
         <v>93</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>20</v>
@@ -18164,7 +18169,7 @@
         <v>20</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -18185,10 +18190,10 @@
         <v>20</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AO129" t="s" s="2">
         <v>20</v>
@@ -18199,10 +18204,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18225,19 +18230,19 @@
         <v>93</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>20</v>
@@ -18286,7 +18291,7 @@
         <v>20</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -18307,10 +18312,10 @@
         <v>20</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AO130" t="s" s="2">
         <v>20</v>
@@ -18321,10 +18326,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18347,19 +18352,19 @@
         <v>93</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>440</v>
+        <v>602</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>20</v>
@@ -18396,7 +18401,7 @@
         <v>20</v>
       </c>
       <c r="AB131" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="AC131" s="2"/>
       <c r="AD131" t="s" s="2">
@@ -18406,7 +18411,7 @@
         <v>198</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -18424,30 +18429,30 @@
         <v>20</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AO131" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP131" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="D132" t="s" s="2">
         <v>20</v>
@@ -18469,19 +18474,19 @@
         <v>93</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>440</v>
+        <v>602</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>20</v>
@@ -18530,7 +18535,7 @@
         <v>20</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -18548,27 +18553,27 @@
         <v>20</v>
       </c>
       <c r="AL132" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AO132" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP132" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18591,13 +18596,13 @@
         <v>20</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -18648,7 +18653,7 @@
         <v>20</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -18672,7 +18677,7 @@
         <v>20</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO133" t="s" s="2">
         <v>20</v>
@@ -18683,10 +18688,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18715,7 +18720,7 @@
         <v>139</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N134" t="s" s="2">
         <v>141</v>
@@ -18756,10 +18761,10 @@
         <v>20</v>
       </c>
       <c r="AB134" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AC134" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AD134" t="s" s="2">
         <v>20</v>
@@ -18768,7 +18773,7 @@
         <v>198</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -18792,7 +18797,7 @@
         <v>20</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>20</v>
@@ -18803,10 +18808,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18829,19 +18834,19 @@
         <v>93</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>20</v>
@@ -18890,7 +18895,7 @@
         <v>20</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -18911,10 +18916,10 @@
         <v>20</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>20</v>
@@ -18925,10 +18930,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18954,20 +18959,20 @@
         <v>112</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q136" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="R136" t="s" s="2">
         <v>20</v>
@@ -18991,10 +18996,10 @@
         <v>181</v>
       </c>
       <c r="Y136" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="Z136" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="AA136" t="s" s="2">
         <v>20</v>
@@ -19012,7 +19017,7 @@
         <v>20</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -19033,10 +19038,10 @@
         <v>20</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="AN136" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="AO136" t="s" s="2">
         <v>20</v>
@@ -19047,10 +19052,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19073,17 +19078,17 @@
         <v>93</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="N137" s="2"/>
       <c r="O137" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>20</v>
@@ -19132,7 +19137,7 @@
         <v>20</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -19153,10 +19158,10 @@
         <v>20</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="AN137" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="AO137" t="s" s="2">
         <v>20</v>
@@ -19167,10 +19172,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19196,14 +19201,14 @@
         <v>106</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>20</v>
@@ -19213,7 +19218,7 @@
         <v>20</v>
       </c>
       <c r="S138" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="T138" t="s" s="2">
         <v>20</v>
@@ -19252,7 +19257,7 @@
         <v>20</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -19261,7 +19266,7 @@
         <v>92</v>
       </c>
       <c r="AI138" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="AJ138" t="s" s="2">
         <v>104</v>
@@ -19273,10 +19278,10 @@
         <v>20</v>
       </c>
       <c r="AM138" t="s" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="AN138" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="AO138" t="s" s="2">
         <v>20</v>
@@ -19287,10 +19292,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19316,16 +19321,16 @@
         <v>112</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="O139" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>20</v>
@@ -19335,7 +19340,7 @@
         <v>20</v>
       </c>
       <c r="S139" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="T139" t="s" s="2">
         <v>20</v>
@@ -19374,7 +19379,7 @@
         <v>20</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
@@ -19395,10 +19400,10 @@
         <v>20</v>
       </c>
       <c r="AM139" t="s" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="AN139" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="AO139" t="s" s="2">
         <v>20</v>
@@ -19409,10 +19414,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19438,16 +19443,16 @@
         <v>203</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="O140" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>20</v>
@@ -19472,13 +19477,13 @@
         <v>20</v>
       </c>
       <c r="X140" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Y140" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="Z140" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AA140" t="s" s="2">
         <v>20</v>
@@ -19496,7 +19501,7 @@
         <v>20</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -19505,7 +19510,7 @@
         <v>92</v>
       </c>
       <c r="AI140" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="AJ140" t="s" s="2">
         <v>104</v>
@@ -19520,7 +19525,7 @@
         <v>135</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="AO140" t="s" s="2">
         <v>20</v>
@@ -19531,14 +19536,14 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E141" s="2"/>
       <c r="F141" t="s" s="2">
@@ -19560,16 +19565,16 @@
         <v>203</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="O141" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>20</v>
@@ -19594,13 +19599,13 @@
         <v>20</v>
       </c>
       <c r="X141" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Y141" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="Z141" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>20</v>
@@ -19618,7 +19623,7 @@
         <v>20</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -19636,27 +19641,27 @@
         <v>20</v>
       </c>
       <c r="AL141" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AO141" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP141" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19682,16 +19687,16 @@
         <v>82</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="O142" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>20</v>
@@ -19740,7 +19745,7 @@
         <v>20</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
@@ -19761,10 +19766,10 @@
         <v>20</v>
       </c>
       <c r="AM142" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="AN142" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AO142" t="s" s="2">
         <v>20</v>

--- a/docs/StructureDefinition-PASportObservationGaitCycle.xlsx
+++ b/docs/StructureDefinition-PASportObservationGaitCycle.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T13:32:15+08:00</t>
+    <t>2026-04-03T21:17:06+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PASportObservationGaitCycle.xlsx
+++ b/docs/StructureDefinition-PASportObservationGaitCycle.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-03T21:17:06+08:00</t>
+    <t>2026-06-25T08:48:04+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
